--- a/create_forecast_basic/future/bau/Intermediates/240703_pop_2045_bau.xlsx
+++ b/create_forecast_basic/future/bau/Intermediates/240703_pop_2045_bau.xlsx
@@ -5356,7 +5356,7 @@
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="n">
-        <v>1444.080822634002</v>
+        <v>1444.080822634</v>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr"/>
@@ -5381,7 +5381,7 @@
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="n">
-        <v>4412.522397006568</v>
+        <v>4412.522397006571</v>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr"/>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
-        <v>3901.367990122833</v>
+        <v>3901.367990122837</v>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr"/>
@@ -5431,7 +5431,7 @@
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="n">
-        <v>17983.19477202056</v>
+        <v>17983.19477202055</v>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr"/>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="n">
-        <v>10199.10228034708</v>
+        <v>10199.10228034707</v>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr"/>
@@ -5556,7 +5556,7 @@
       </c>
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="n">
-        <v>17699.37028065899</v>
+        <v>17699.370280659</v>
       </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr"/>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="B102" t="inlineStr"/>
       <c r="C102" t="n">
-        <v>11418.56142226344</v>
+        <v>11418.56142226343</v>
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr"/>
@@ -5606,7 +5606,7 @@
       </c>
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="n">
-        <v>46872.6379749994</v>
+        <v>46872.63797499942</v>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr"/>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="n">
-        <v>34651.02399823596</v>
+        <v>34651.02399823593</v>
       </c>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr"/>
@@ -5681,7 +5681,7 @@
       </c>
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="n">
-        <v>11597.75028165577</v>
+        <v>11597.75028165578</v>
       </c>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr"/>
@@ -5706,7 +5706,7 @@
       </c>
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="n">
-        <v>1703.392588127761</v>
+        <v>1703.392588127763</v>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr"/>
@@ -5731,7 +5731,7 @@
       </c>
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="n">
-        <v>8345.658044192278</v>
+        <v>8345.65804419228</v>
       </c>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr"/>
@@ -5756,7 +5756,7 @@
       </c>
       <c r="B109" t="inlineStr"/>
       <c r="C109" t="n">
-        <v>2903.105744298144</v>
+        <v>2903.105744298145</v>
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr"/>
@@ -5781,7 +5781,7 @@
       </c>
       <c r="B110" t="inlineStr"/>
       <c r="C110" t="n">
-        <v>2633.019057977311</v>
+        <v>2633.019057977313</v>
       </c>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr"/>
@@ -5806,7 +5806,7 @@
       </c>
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="n">
-        <v>15044.84024666124</v>
+        <v>15044.84024666123</v>
       </c>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr"/>
@@ -5856,7 +5856,7 @@
       </c>
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="n">
-        <v>11624.59464468694</v>
+        <v>11624.59464468695</v>
       </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr"/>
@@ -5931,7 +5931,7 @@
       </c>
       <c r="B116" t="inlineStr"/>
       <c r="C116" t="n">
-        <v>3548.080350829619</v>
+        <v>3548.080350829617</v>
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr"/>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="n">
-        <v>8810.887690708556</v>
+        <v>8810.88769070854</v>
       </c>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr"/>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="n">
-        <v>8128.135535092119</v>
+        <v>8128.135535092116</v>
       </c>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr"/>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="B123" t="inlineStr"/>
       <c r="C123" t="n">
-        <v>43393.29712199598</v>
+        <v>43393.29712199599</v>
       </c>
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr"/>
@@ -6131,7 +6131,7 @@
       </c>
       <c r="B124" t="inlineStr"/>
       <c r="C124" t="n">
-        <v>11595.35987802437</v>
+        <v>11595.35987802438</v>
       </c>
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr"/>
@@ -6156,7 +6156,7 @@
       </c>
       <c r="B125" t="inlineStr"/>
       <c r="C125" t="n">
-        <v>14653.03333363161</v>
+        <v>14653.0333336316</v>
       </c>
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr"/>
@@ -6181,7 +6181,7 @@
       </c>
       <c r="B126" t="inlineStr"/>
       <c r="C126" t="n">
-        <v>31470.66957178908</v>
+        <v>31470.66957178909</v>
       </c>
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr"/>
@@ -6256,7 +6256,7 @@
       </c>
       <c r="B129" t="inlineStr"/>
       <c r="C129" t="n">
-        <v>7041.977550501426</v>
+        <v>7041.97755050143</v>
       </c>
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr"/>
@@ -6281,7 +6281,7 @@
       </c>
       <c r="B130" t="inlineStr"/>
       <c r="C130" t="n">
-        <v>5935.048125165347</v>
+        <v>5935.048125165346</v>
       </c>
       <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr"/>
@@ -6356,7 +6356,7 @@
       </c>
       <c r="B133" t="inlineStr"/>
       <c r="C133" t="n">
-        <v>4657.342380594495</v>
+        <v>4657.342380594494</v>
       </c>
       <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr"/>
@@ -6381,7 +6381,7 @@
       </c>
       <c r="B134" t="inlineStr"/>
       <c r="C134" t="n">
-        <v>735.6036983263888</v>
+        <v>735.6036983263886</v>
       </c>
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr"/>
@@ -6506,7 +6506,7 @@
       </c>
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="n">
-        <v>4199.883524368045</v>
+        <v>4199.883524368048</v>
       </c>
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr"/>
@@ -6581,7 +6581,7 @@
       </c>
       <c r="B142" t="inlineStr"/>
       <c r="C142" t="n">
-        <v>2763.651896216311</v>
+        <v>2763.65189621631</v>
       </c>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr"/>
@@ -6806,7 +6806,7 @@
       </c>
       <c r="B151" t="inlineStr"/>
       <c r="C151" t="n">
-        <v>4690.264028814986</v>
+        <v>4690.264028814987</v>
       </c>
       <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr"/>
@@ -6831,7 +6831,7 @@
       </c>
       <c r="B152" t="inlineStr"/>
       <c r="C152" t="n">
-        <v>7943.44135986974</v>
+        <v>7943.441359869738</v>
       </c>
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr"/>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="B153" t="inlineStr"/>
       <c r="C153" t="n">
-        <v>3934.831287525574</v>
+        <v>3934.831287525576</v>
       </c>
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr"/>
@@ -6956,7 +6956,7 @@
       </c>
       <c r="B157" t="inlineStr"/>
       <c r="C157" t="n">
-        <v>3148.423261427506</v>
+        <v>3148.423261427505</v>
       </c>
       <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr"/>
@@ -6981,7 +6981,7 @@
       </c>
       <c r="B158" t="inlineStr"/>
       <c r="C158" t="n">
-        <v>4877.257729121437</v>
+        <v>4877.257729121438</v>
       </c>
       <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr"/>
@@ -7031,7 +7031,7 @@
       </c>
       <c r="B160" t="inlineStr"/>
       <c r="C160" t="n">
-        <v>5454.23730935279</v>
+        <v>5454.237309352789</v>
       </c>
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr"/>
@@ -7056,7 +7056,7 @@
       </c>
       <c r="B161" t="inlineStr"/>
       <c r="C161" t="n">
-        <v>6258.93970246337</v>
+        <v>6258.939702463372</v>
       </c>
       <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr"/>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="B163" t="inlineStr"/>
       <c r="C163" t="n">
-        <v>9273.087630376784</v>
+        <v>9273.08763037678</v>
       </c>
       <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr"/>
@@ -7131,7 +7131,7 @@
       </c>
       <c r="B164" t="inlineStr"/>
       <c r="C164" t="n">
-        <v>6493.841006380268</v>
+        <v>6493.841006380267</v>
       </c>
       <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr"/>
@@ -7156,7 +7156,7 @@
       </c>
       <c r="B165" t="inlineStr"/>
       <c r="C165" t="n">
-        <v>8122.207414731325</v>
+        <v>8122.207414731324</v>
       </c>
       <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr"/>
@@ -7181,7 +7181,7 @@
       </c>
       <c r="B166" t="inlineStr"/>
       <c r="C166" t="n">
-        <v>62254.81556662309</v>
+        <v>62254.81556662313</v>
       </c>
       <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr"/>
@@ -7206,7 +7206,7 @@
       </c>
       <c r="B167" t="inlineStr"/>
       <c r="C167" t="n">
-        <v>53962.0471183341</v>
+        <v>53962.04711833408</v>
       </c>
       <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr"/>
@@ -7231,7 +7231,7 @@
       </c>
       <c r="B168" t="inlineStr"/>
       <c r="C168" t="n">
-        <v>57616.60941373192</v>
+        <v>57616.60941373189</v>
       </c>
       <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr"/>
@@ -7256,7 +7256,7 @@
       </c>
       <c r="B169" t="inlineStr"/>
       <c r="C169" t="n">
-        <v>61606.43346297648</v>
+        <v>61606.43346297649</v>
       </c>
       <c r="D169" t="inlineStr"/>
       <c r="E169" t="inlineStr"/>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="B170" t="inlineStr"/>
       <c r="C170" t="n">
-        <v>74898.71422240316</v>
+        <v>74898.71422240317</v>
       </c>
       <c r="D170" t="inlineStr"/>
       <c r="E170" t="inlineStr"/>
@@ -7306,7 +7306,7 @@
       </c>
       <c r="B171" t="inlineStr"/>
       <c r="C171" t="n">
-        <v>93618.99641204368</v>
+        <v>93618.99641204359</v>
       </c>
       <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr"/>
@@ -7331,7 +7331,7 @@
       </c>
       <c r="B172" t="inlineStr"/>
       <c r="C172" t="n">
-        <v>1976.098917533337</v>
+        <v>1976.098917533336</v>
       </c>
       <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr"/>
@@ -7356,7 +7356,7 @@
       </c>
       <c r="B173" t="inlineStr"/>
       <c r="C173" t="n">
-        <v>17292.06600795573</v>
+        <v>17292.06600795571</v>
       </c>
       <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr"/>
@@ -7556,7 +7556,7 @@
       </c>
       <c r="B181" t="inlineStr"/>
       <c r="C181" t="n">
-        <v>9973.504387042964</v>
+        <v>9973.504387042969</v>
       </c>
       <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr"/>
@@ -7606,7 +7606,7 @@
       </c>
       <c r="B183" t="inlineStr"/>
       <c r="C183" t="n">
-        <v>3749.14178402223</v>
+        <v>3749.141784022229</v>
       </c>
       <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr"/>
@@ -7631,7 +7631,7 @@
       </c>
       <c r="B184" t="inlineStr"/>
       <c r="C184" t="n">
-        <v>4960.237872431137</v>
+        <v>4960.237872431138</v>
       </c>
       <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr"/>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="B187" t="inlineStr"/>
       <c r="C187" t="n">
-        <v>12625.18061057271</v>
+        <v>12625.1806105727</v>
       </c>
       <c r="D187" t="inlineStr"/>
       <c r="E187" t="inlineStr"/>
@@ -7731,7 +7731,7 @@
       </c>
       <c r="B188" t="inlineStr"/>
       <c r="C188" t="n">
-        <v>16309.7897959832</v>
+        <v>16309.78979598319</v>
       </c>
       <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr"/>
@@ -7806,7 +7806,7 @@
       </c>
       <c r="B191" t="inlineStr"/>
       <c r="C191" t="n">
-        <v>5882.23659663767</v>
+        <v>5882.236596637671</v>
       </c>
       <c r="D191" t="inlineStr"/>
       <c r="E191" t="inlineStr"/>
@@ -7856,7 +7856,7 @@
       </c>
       <c r="B193" t="inlineStr"/>
       <c r="C193" t="n">
-        <v>31913.94072700108</v>
+        <v>31913.94072700106</v>
       </c>
       <c r="D193" t="inlineStr"/>
       <c r="E193" t="inlineStr"/>
@@ -7931,7 +7931,7 @@
       </c>
       <c r="B196" t="inlineStr"/>
       <c r="C196" t="n">
-        <v>19659.32741983673</v>
+        <v>19659.32741983675</v>
       </c>
       <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr"/>
@@ -7956,7 +7956,7 @@
       </c>
       <c r="B197" t="inlineStr"/>
       <c r="C197" t="n">
-        <v>78383.27457355097</v>
+        <v>78383.27457355105</v>
       </c>
       <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr"/>
@@ -8106,7 +8106,7 @@
       </c>
       <c r="B203" t="inlineStr"/>
       <c r="C203" t="n">
-        <v>13573.5575709857</v>
+        <v>13573.55757098569</v>
       </c>
       <c r="D203" t="inlineStr"/>
       <c r="E203" t="inlineStr"/>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="B205" t="inlineStr"/>
       <c r="C205" t="n">
-        <v>25347.97654026994</v>
+        <v>25347.97654026995</v>
       </c>
       <c r="D205" t="inlineStr"/>
       <c r="E205" t="inlineStr"/>
@@ -8181,7 +8181,7 @@
       </c>
       <c r="B206" t="inlineStr"/>
       <c r="C206" t="n">
-        <v>32362.97343742904</v>
+        <v>32362.97343742902</v>
       </c>
       <c r="D206" t="inlineStr"/>
       <c r="E206" t="inlineStr"/>
@@ -8206,7 +8206,7 @@
       </c>
       <c r="B207" t="inlineStr"/>
       <c r="C207" t="n">
-        <v>45289.63472859195</v>
+        <v>45289.63472859196</v>
       </c>
       <c r="D207" t="inlineStr"/>
       <c r="E207" t="inlineStr"/>
@@ -8281,7 +8281,7 @@
       </c>
       <c r="B210" t="inlineStr"/>
       <c r="C210" t="n">
-        <v>9261.975369723456</v>
+        <v>9261.975369723457</v>
       </c>
       <c r="D210" t="inlineStr"/>
       <c r="E210" t="inlineStr"/>
@@ -8306,7 +8306,7 @@
       </c>
       <c r="B211" t="inlineStr"/>
       <c r="C211" t="n">
-        <v>11127.81900875665</v>
+        <v>11127.81900875666</v>
       </c>
       <c r="D211" t="inlineStr"/>
       <c r="E211" t="inlineStr"/>
@@ -8331,7 +8331,7 @@
       </c>
       <c r="B212" t="inlineStr"/>
       <c r="C212" t="n">
-        <v>7393.235028499726</v>
+        <v>7393.235028499724</v>
       </c>
       <c r="D212" t="inlineStr"/>
       <c r="E212" t="inlineStr"/>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="B213" t="inlineStr"/>
       <c r="C213" t="n">
-        <v>3983.447116632477</v>
+        <v>3983.447116632479</v>
       </c>
       <c r="D213" t="inlineStr"/>
       <c r="E213" t="inlineStr"/>
@@ -8431,7 +8431,7 @@
       </c>
       <c r="B216" t="inlineStr"/>
       <c r="C216" t="n">
-        <v>4495.305652546583</v>
+        <v>4495.305652546584</v>
       </c>
       <c r="D216" t="inlineStr"/>
       <c r="E216" t="inlineStr"/>
@@ -8506,7 +8506,7 @@
       </c>
       <c r="B219" t="inlineStr"/>
       <c r="C219" t="n">
-        <v>11724.78187801683</v>
+        <v>11724.78187801682</v>
       </c>
       <c r="D219" t="inlineStr"/>
       <c r="E219" t="inlineStr"/>
@@ -8731,7 +8731,7 @@
       </c>
       <c r="B228" t="inlineStr"/>
       <c r="C228" t="n">
-        <v>93861.23325926118</v>
+        <v>93861.23325926115</v>
       </c>
       <c r="D228" t="inlineStr"/>
       <c r="E228" t="inlineStr"/>
@@ -8881,7 +8881,7 @@
       </c>
       <c r="B234" t="inlineStr"/>
       <c r="C234" t="n">
-        <v>14082.38300421123</v>
+        <v>14082.38300421121</v>
       </c>
       <c r="D234" t="inlineStr"/>
       <c r="E234" t="inlineStr"/>
@@ -9006,7 +9006,7 @@
       </c>
       <c r="B239" t="inlineStr"/>
       <c r="C239" t="n">
-        <v>8140.752313540292</v>
+        <v>8140.752313540289</v>
       </c>
       <c r="D239" t="inlineStr"/>
       <c r="E239" t="inlineStr"/>
@@ -9056,7 +9056,7 @@
       </c>
       <c r="B241" t="inlineStr"/>
       <c r="C241" t="n">
-        <v>50679.54837240438</v>
+        <v>50679.54837240437</v>
       </c>
       <c r="D241" t="inlineStr"/>
       <c r="E241" t="inlineStr"/>
@@ -9081,7 +9081,7 @@
       </c>
       <c r="B242" t="inlineStr"/>
       <c r="C242" t="n">
-        <v>34747.33964562143</v>
+        <v>34747.33964562141</v>
       </c>
       <c r="D242" t="inlineStr"/>
       <c r="E242" t="inlineStr"/>
@@ -9131,7 +9131,7 @@
       </c>
       <c r="B244" t="inlineStr"/>
       <c r="C244" t="n">
-        <v>48056.83231222583</v>
+        <v>48056.83231222588</v>
       </c>
       <c r="D244" t="inlineStr"/>
       <c r="E244" t="inlineStr"/>
@@ -9256,7 +9256,7 @@
       </c>
       <c r="B249" t="inlineStr"/>
       <c r="C249" t="n">
-        <v>35996.89549938603</v>
+        <v>35996.89549938602</v>
       </c>
       <c r="D249" t="inlineStr"/>
       <c r="E249" t="inlineStr"/>
